--- a/extenbooks/XS1602.xlsx
+++ b/extenbooks/XS1602.xlsx
@@ -729,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -836,7 +836,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>book_period_validated</t>
+          <t>pending:faithful_kt_source</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Status**: CULLED (do not publish) — reverse-engineered proxy, 2026-06-11 reconciliation</t>
+          <t>**Status**: pending:faithful_kt_source</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Approximation: `(govt_consumption - tax_revenue) / 100` from World Bank fiscal Turkey.</t>
+          <t>&gt; CULLED / DO NOT PUBLISH (`publish: false`, `triage.verdict: cull`). The `pending:faithful_kt_source`</t>
         </is>
       </c>
     </row>
@@ -950,19 +950,23 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Range [-5.43%, -0.04%].</t>
+          <t>&gt; status reconciles this DPR with the registry (WP-E review 2026-07-01): the prior registry</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>&gt; `book_period_validated` was a FALSE validation claim. The series is a reverse-engineered World-Bank</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>**CORRECTION (2026-06-11)**: This is NOT the Karabacak &amp; Tonak NSW methodology</t>
+          <t>&gt; (govt_consumption − tax_revenue) proxy with year-point reference_values equal to its own output</t>
         </is>
       </c>
     </row>
@@ -970,7 +974,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>(B = E1 + E2*ls, T = T1 + T2*ls with sector decomposition). The processor docstring</t>
+          <t>&gt; (tautological); V03 currently FAILS (n_negative 30 vs 40 — 10 NaN years: 1982, 1999-2007). Blocked</t>
         </is>
       </c>
     </row>
@@ -978,7 +982,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>states the crude govt-consumption-minus-tax formula was chosen because it "gives</t>
+          <t>&gt; pending faithful re-derivation from K&amp;T 2022's NSW decomposition (see `triage.republish_condition`).</t>
         </is>
       </c>
     </row>
@@ -986,7 +990,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>negative values ... matching K&amp;T's NSW negativity finding" — i.e. it was reverse-</t>
+          <t>&gt; T6b attempt = BLOCKED-G2 (K&amp;T publish no annual NSW table — values in Figure 9 only; paper paywalled).</t>
         </is>
       </c>
     </row>
@@ -994,23 +998,19 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>engineered to reproduce a known headline, not derived from the source method. The</t>
+          <t>&gt; Old status: `book_period_validated`.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>research JSON's claimed TurkStat/SGK/Ministry fiscal sourcing is not implemented in</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>code, and its "2007-2019 NaN" claim is false (the chopped CSV has values for 2008-2019;</t>
+          <t>Approximation: `(govt_consumption - tax_revenue) / 100` from World Bank fiscal Turkey.</t>
         </is>
       </c>
     </row>
@@ -1018,37 +1018,105 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>only 1982 and 1999-2007 are NaN, driven by missing WB tax_revenue rows). Depends on the</t>
+          <t>Range [-5.43%, -0.04%].</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>culled XS1601. Culled pending a faithful re-implementation.</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>**CORRECTION (2026-06-11)**: This is NOT the Karabacak &amp; Tonak NSW methodology</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>(B = E1 + E2*ls, T = T1 + T2*ls with sector decomposition). The processor docstring</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>states the crude govt-consumption-minus-tax formula was chosen because it "gives</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
+        <is>
+          <t>negative values ... matching K&amp;T's NSW negativity finding" — i.e. it was reverse-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>engineered to reproduce a known headline, not derived from the source method. The</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>research JSON's claimed TurkStat/SGK/Ministry fiscal sourcing is not implemented in</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>code, and its "2007-2019 NaN" claim is false (the chopped CSV has values for 2008-2019;</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>only 1982 and 1999-2007 are NaN, driven by missing WB tax_revenue rows). Depends on the</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>culled XS1601. Culled pending a faithful re-implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1065,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1103,7 +1171,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1188,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1205,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1222,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1239,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1256,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1273,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1290,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1307,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1324,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1273,126 +1341,126 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>definition</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NSW/GDP ratio = (B - T) / GDP, where B = E1 + E2*ls (benefits to labor = direct labor benefits + mixed expenditures allocated by labor share), T = T1 + T2*ls (taxes from labor = direct labor taxes + mixed taxes allocated by labor share), and ls = XS1601 (Turkish labor share). A negative ratio means workers are net contributors to the state — they pay more in taxes than they receive in benefits. This is the primary output of the Shaikh-Tonak NSW framework as applied to Turkey by Karabacak &amp; Tonak (2022).</t>
+          <t>K&amp;T 2022 report the NSW/GDP ratio ONLY as an aggregate and via Figure 9 (annual series shown as a chart, NOT tabulated). Independent K&amp;T anchors: mean NSW/GDP = -1.13% (-0.0113); NSW negative for ALL 40 years (1980-2019); 1980 ~ -1% of GDP (Figure 9); worst 2014-2019 reaching -2% to -2.5%. NOTE: the CULLED WB (govt_consumption - tax_revenue) proxy XS1602 covers only 30 of 40 years (10 NaN: 1982, 1999-2007), has mean -0.0299, and its 2019 value -0.0129 is far milder than the paper's ~-0.02/-0.025 worst-period reading - diverging from the K&amp;T anchor in coverage and magnitude.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KT_2022, Sections 3.3, 4.5; Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>Karabacak &amp; Tonak 2022, RRPE 54(4):479-500, Abstract/Section 5.1 (mean NSW/GDP = -1.13%, negative for all 40 years) + Figure 9 (NSW ratio time series)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>key_result</t>
+          <t>definition</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Main finding of Karabacak &amp; Tonak (2022): NSW was NEGATIVE for all 40 years (1980-2019). Mean NSW/GDP = -0.0113 (-1.13% of GDP). Paper reports -0.011 (rounded). ST2 series XS1602 achieves mean = -0.0098 after [internal-decision-record] fix (TurkStat labor share replaces SBB proxy). The remaining gap of ~0.0015 is attributable to: (a) the 2007-2019 period having NaN values in XS1602 (reducing the denominator of the mean), (b) TurkStat Table 20.37 economy-wide ls vs. the paper's productive-sector ls, and (c) benefit/tax level data not yet fully disaggregated from Turkish ministry sources. The direction, sign, and order of magnitude match the paper.</t>
+          <t>NSW/GDP ratio = (B - T) / GDP, where B = E1 + E2*ls (benefits to labor = direct labor benefits + mixed expenditures allocated by labor share), T = T1 + T2*ls (taxes from labor = direct labor taxes + mixed taxes allocated by labor share), and ls = XS1601 (Turkish labor share). A negative ratio means workers are net contributors to the state — they pay more in taxes than they receive in benefits. This is the primary output of the Shaikh-Tonak NSW framework as applied to Turkey by Karabacak &amp; Tonak (2022).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KT_2022, Section 5.1 and Abstract; [internal-decision-log]#[internal-decision-record]; Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KT_2022, Sections 3.3, 4.5; Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sign_characterization</t>
+          <t>key_result</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NSW was negative for ALL 40 years (1980-2019) — 100% of observations. No year had a positive NSW. This is the central empirical claim of KT (2022): the Turkish 'pseudo-welfare state' extracts more from workers than it returns. ST2 XS1602 must reproduce this universal-negative property. Any year with a computed positive value should be flagged as a data error, not accepted as consistent with the source.</t>
+          <t>Main finding of Karabacak &amp; Tonak (2022): NSW was NEGATIVE for all 40 years (1980-2019). Mean NSW/GDP = -0.0113 (-1.13% of GDP). Paper reports -0.011 (rounded). ST2 series XS1602 achieves mean = -0.0098 after [internal-decision-record] fix (TurkStat labor share replaces SBB proxy). The remaining gap of ~0.0015 is attributable to: (a) the 2007-2019 period having NaN values in XS1602 (reducing the denominator of the mean), (b) TurkStat Table 20.37 economy-wide ls vs. the paper's productive-sector ls, and (c) benefit/tax level data not yet fully disaggregated from Turkish ministry sources. The direction, sign, and order of magnitude match the paper.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KT_2022, Sections 1 (Preview of Findings) and 5.1; Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KT_2022, Section 5.1 and Abstract; [internal-decision-log]#[internal-decision-record]; Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>period_breakdown</t>
+          <t>sign_characterization</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NSW by sub-period (from KT 2022 Section 5.4 and 5.5): 1980-1989 (Military/Ozal era): avg -1.0% of GDP. 1990-2001 (pre-AKP coalitions): avg -0.8% of GDP — the best period for workers, least negative NSW. 2002-2008 (early AKP, economic boom): avg -1.0% of GDP. 2009-2013 (post-financial crisis recovery): avg -0.9% of GDP. 2014-2019 (AKP austerity): avg -1.8% of GDP — WORST period. Pre-AKP average (1980-2001): -0.93%. AKP average (2002-2019): -1.24%. Best single year: 1998 (-0.5%). Worst single year: 2018 (-2.5%).</t>
+          <t>NSW was negative for ALL 40 years (1980-2019) — 100% of observations. No year had a positive NSW. This is the central empirical claim of KT (2022): the Turkish 'pseudo-welfare state' extracts more from workers than it returns. ST2 XS1602 must reproduce this universal-negative property. Any year with a computed positive value should be flagged as a data error, not accepted as consistent with the source.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KT_2022, Section 5.4 and 5.5; Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KT_2022, Sections 1 (Preview of Findings) and 5.1; Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>data_sources_paper</t>
+          <t>period_breakdown</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KT (2022) Section 4.1 lists primary data sources used to construct NSW: Government expenditures from Ministry of Treasury and Finance (budget execution reports), Social Security Institution (SGK), Ministry of National Education, Ministry of Health. Tax revenues from Revenue Administration (Gelir Idaresi), Customs Administration, SGK. National accounts from TurkStat (GDP, NDP, compensation of employees by sector). Labor market data from TurkStat Household Labor Force Survey. Time period: 1980-2019 (40 years). Note: Turkey's fiscal statistics improved significantly after 2006 (IMF-mandated reforms); pre-2006 data required reconciliation.</t>
+          <t>NSW by sub-period (from KT 2022 Section 5.4 and 5.5): 1980-1989 (Military/Ozal era): avg -1.0% of GDP. 1990-2001 (pre-AKP coalitions): avg -0.8% of GDP — the best period for workers, least negative NSW. 2002-2008 (early AKP, economic boom): avg -1.0% of GDP. 2009-2013 (post-financial crisis recovery): avg -0.9% of GDP. 2014-2019 (AKP austerity): avg -1.8% of GDP — WORST period. Pre-AKP average (1980-2001): -0.93%. AKP average (2002-2019): -1.24%. Best single year: 1998 (-0.5%). Worst single year: 2018 (-2.5%).</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KT_2022, Section 4.1; Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KT_2022, Section 5.4 and 5.5; Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>data_gap</t>
+          <t>data_sources_paper</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>XS1602 coverage is limited to 1980-2006 (27 years) because XS1601 (labor share, the ls parameter) only has real data through 2006 from TurkStat Table 20.37. Years 2007-2019 are NaN per [internal-decision-record] (no-synthetic-data policy). The [internal-decision-record] note confirms: 'Years 2007-2019 are NaN per [internal-decision-record] (no synthetic fill).' The paper's full 1980-2019 series cannot be reproduced without real ls and fiscal data for 2007-2019. OECD data was considered for 2007-2019 but only has tax/GDP ratios, not compensation-of-employees data needed for ls.</t>
+          <t>KT (2022) Section 4.1 lists primary data sources used to construct NSW: Government expenditures from Ministry of Treasury and Finance (budget execution reports), Social Security Institution (SGK), Ministry of National Education, Ministry of Health. Tax revenues from Revenue Administration (Gelir Idaresi), Customs Administration, SGK. National accounts from TurkStat (GDP, NDP, compensation of employees by sector). Labor market data from TurkStat Household Labor Force Survey. Time period: 1980-2019 (40 years). Note: Turkey's fiscal statistics improved significantly after 2006 (IMF-mandated reforms); pre-2006 data required reconciliation.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[internal-decision-log]#[internal-decision-record]; [internal-decision-log]#[internal-decision-record]</t>
+          <t>KT_2022, Section 4.1; Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>data_gap</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[internal-decision-record] (2026-05-06): Switching XS1601 from SBB Personel proxy to TurkStat Table 20.37 improved XS1602 mean from -0.0025 to -0.0098 (paper target: -0.011). The prior proxy calibration artifacts — a '*0.3' transfer multiplier and '*1.1' tax multiplier in P18 Path A/B — have been removed. These were not part of the KT (2022) methodology; they were correction factors patching the wrong proxy. With TurkStat ls, the raw NSW formula (B - T)/GDP produces -0.0098, within 13% of the paper's reported -0.011.</t>
+          <t>XS1602 coverage is limited to 1980-2006 (27 years) because XS1601 (labor share, the ls parameter) only has real data through 2006 from TurkStat Table 20.37. Years 2007-2019 are NaN per [internal-decision-record] (no-synthetic-data policy). The [internal-decision-record] note confirms: 'Years 2007-2019 are NaN per [internal-decision-record] (no synthetic fill).' The paper's full 1980-2019 series cannot be reproduced without real ls and fiscal data for 2007-2019. OECD data was considered for 2007-2019 but only has tax/GDP ratios, not compensation-of-employees data needed for ls.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[internal-decision-log]#[internal-decision-record]</t>
+          <t>[internal-decision-log]#[internal-decision-record]; [internal-decision-log]#[internal-decision-record]</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1472,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[internal-decision-record] (2026-05-03): No-synthetic-data policy. XS1602 was previously generated using synthetic XS1601 values (np.random linear trend). This is prohibited. The 2007-2019 gap must remain as NaN. XS1602 must not be filled with modeled, estimated, or interpolated values for 2007-2019 absent real fiscal and labor share data from TurkStat or equivalent official sources extracted via HDARP or API with full provenance.</t>
+          <t>[internal-decision-record] (2026-05-06): Switching XS1601 from SBB Personel proxy to TurkStat Table 20.37 improved XS1602 mean from -0.0025 to -0.0098 (paper target: -0.011). The prior proxy calibration artifacts — a '*0.3' transfer multiplier and '*1.1' tax multiplier in P18 Path A/B — have been removed. These were not part of the KT (2022) methodology; they were correction factors patching the wrong proxy. With TurkStat ls, the raw NSW formula (B - T)/GDP produces -0.0098, within 13% of the paper's reported -0.011.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1416,80 +1484,89 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>decision_reference</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NSW calculation procedure (KT 2022 Section 4.5): Step 1: B = E1 + E2*ls (benefits to labor). E1 = direct labor benefits (pensions, disability/survivor benefits, unemployment insurance, public education, social assistance, public health). E2 = mixed expenditures (general public services, defense, infrastructure, environment, culture) allocated by ls. Step 2: T = T1 + T2*ls (taxes from labor). T1 = direct taxes (personal income tax on wages, employee social security contributions). T2 = indirect/mixed taxes (VAT, Special Consumption Tax, customs duties, property taxes, corporate income tax) allocated by ls. T3 = taxes on capital (non-wage income tax, dividends, interest, rent, capital gains) — excluded from T. Step 3: NSW = B - T. Step 4: NSW_ratio = NSW / GDP.</t>
+          <t>[internal-decision-record] (2026-05-03): No-synthetic-data policy. XS1602 was previously generated using synthetic XS1601 values (np.random linear trend). This is prohibited. The 2007-2019 gap must remain as NaN. XS1602 must not be filled with modeled, estimated, or interpolated values for 2007-2019 absent real fiscal and labor share data from TurkStat or equivalent official sources extracted via HDARP or API with full provenance.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KT_2022, Sections 4.2-4.5; Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>[internal-decision-log]#[internal-decision-record]</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>validation_target</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Validation benchmark: KT (2022) Abstract and Section 5.1 report mean NSW/GDP = -0.0113 (stated as '-1.13% of GDP'). The paper rounds to '-1.1%' in the Abstract. ST2 achieves -0.0098 after [internal-decision-record] fix. The 0.0015 residual gap is acceptable given: (a) TurkStat total-compensation ls vs. paper's productive-sector ls, (b) 2007-2019 NaN years affecting the mean, (c) benefit/tax source data provenance differences. The sign (negative) and universal negativity (100% of years) are the primary validation criteria. V-layer acceptance range: [-0.008, -0.015].</t>
+          <t>NSW calculation procedure (KT 2022 Section 4.5): Step 1: B = E1 + E2*ls (benefits to labor). E1 = direct labor benefits (pensions, disability/survivor benefits, unemployment insurance, public education, social assistance, public health). E2 = mixed expenditures (general public services, defense, infrastructure, environment, culture) allocated by ls. Step 2: T = T1 + T2*ls (taxes from labor). T1 = direct taxes (personal income tax on wages, employee social security contributions). T2 = indirect/mixed taxes (VAT, Special Consumption Tax, customs duties, property taxes, corporate income tax) allocated by ls. T3 = taxes on capital (non-wage income tax, dividends, interest, rent, capital gains) — excluded from T. Step 3: NSW = B - T. Step 4: NSW_ratio = NSW / GDP.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KT_2022, Abstract and Section 5.1; [internal-decision-log]#[internal-decision-record]; Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+          <t>KT_2022, Sections 4.2-4.5; Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>validation_target</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Validation benchmark: KT (2022) Abstract and Section 5.1 report mean NSW/GDP = -0.0113 (stated as '-1.13% of GDP'). The paper rounds to '-1.1%' in the Abstract. ST2 achieves -0.0098 after [internal-decision-record] fix. The 0.0015 residual gap is acceptable given: (a) TurkStat total-compensation ls vs. paper's productive-sector ls, (b) 2007-2019 NaN years affecting the mean, (c) benefit/tax source data provenance differences. The sign (negative) and universal negativity (100% of years) are the primary validation criteria. V-layer acceptance range: [-0.008, -0.015].</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>KT_2022, Abstract and Section 5.1; [internal-decision-log]#[internal-decision-record]; Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>theoretical_context</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>The NSW framework (Shaikh &amp; Tonak 1987, 1994) measures the net fiscal transfer from the state to labor. When NSW &lt; 0, the state transfers value from labor to capital, raising the effective rate of surplus value above the nominal rate: s/v_eff &gt; s/v_nom. KT (2022) Section 3.6 shows that for Turkey, s/v_eff &gt; s/v_nom for the entire 1980-2019 period. The Turkish state is not a welfare state but a 'worker-subsidized state.' This is consistent with Shaikh-Tonak USA findings, Tsoulfidis-Paitaridis Greece findings, and Moos (2017) multi-country analysis.</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>KT_2022, Sections 2.5, 3.3, 3.6, 6.2; Technical/Knowledge_Base/external_papers/international/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>KT_2022, Sections 2.5, 3.3, 3.6, 6.2; Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2022_Karabacak_Tonak_NSW_Turkey/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>methodology_summary</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>XS1602 = (B - T) / GDP following KT (2022) Section 4.5. B = E1 + E2*ls, T = T1 + T2*ls, ls = XS1601 (TurkStat Table 20.37 labor share). Mean = -0.0098 (paper reports -0.011). Universal negativity (all 40 years negative) is the primary structural validation criterion. Coverage 1980-2006 (27 years real); 2007-2019 are NaN per [internal-decision-record]. SBB proxy calibration artifacts (transfer and tax multipliers) removed per [internal-decision-record].</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>CULLED (2026-06-11 reconciliation): the implemented code (P02_XS1602_turkey_nsw_gdp.py) computes a World Bank (govt_consumption - tax_revenue)/100 proxy reverse-engineered to reproduce the paper's NSW-negative headline, NOT the K&amp;T NSW decomposition this JSON describes. The 2007-2019 NaN claim is also false (chopped has 2008-2019 values). Depends on culled XS1601. Series culled; do not publish.</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1574,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2007-2019 gap: XS1601 has no real data after 2006; years 2007-2019 are NaN per [internal-decision-record]. The full 1980-2019 KT (2022) series cannot be reproduced without additional TurkStat income-approach data for post-2006 years.</t>
+          <t>CULLED (2026-06-11 reconciliation): the implemented code (P02_XS1602_turkey_nsw_gdp.py) computes a World Bank (govt_consumption - tax_revenue)/100 proxy reverse-engineered to reproduce the paper's NSW-negative headline, NOT the K&amp;T NSW decomposition this JSON describes. The 2007-2019 NaN claim is also false (chopped has 2008-2019 values). Depends on culled XS1601. Series culled; do not publish.</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1582,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mean residual: ST2 achieves -0.0098 vs. paper's -0.011. Gap of 0.0015 is within acceptable range given ls methodology differences (total compensation / GDP vs. productive-sector wages / NDP).</t>
+          <t>2007-2019 gap: XS1601 has no real data after 2006; years 2007-2019 are NaN per [internal-decision-record]. The full 1980-2019 KT (2022) series cannot be reproduced without additional TurkStat income-approach data for post-2006 years.</t>
         </is>
       </c>
     </row>
@@ -1513,65 +1590,73 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
+          <t>Mean residual: ST2 achieves -0.0098 vs. paper's -0.011. Gap of 0.0015 is within acceptable range given ls methodology differences (total compensation / GDP vs. productive-sector wages / NDP).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>ls denominator mismatch: TurkStat Table 20.37 uses GDP as denominator; KT (2022) uses NDP. This systematically understates ls, which partially offsets benefit/tax allocation and contributes to the residual gap.</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>cross_references:</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
         <is>
           <t>XS1601</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KT_2022</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Karabacak, Zafer, and E. Ahmet Tonak. 2022. 'The Net Social Wage in Turkey, 1980-2019.' Review of Radical Political Economics 54 (4): 577-605. DOI: 10.1177/04866134221089659.</t>
+          <t>citations:</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ST_1994</t>
+          <t>KT_2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge: Cambridge University Press.</t>
+          <t>Karabacak, Yakup, and E. Ahmet Tonak. 2022. 'The Net Social Wage in Turkey, 1980-2019.' Review of Radical Political Economics 54 (4): 577-605. DOI: 10.1177/04866134221089659.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge: Cambridge University Press.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>TurkStat_2011</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Turkish Statistical Institute (TurkStat). 2011. Statistical Indicators 1923-2011. Table 20.37: Share of Gross Domestic Product by cost components (at current prices), 1980-2006. Ankara: TurkStat. [Digitized via HDARP, chunk_027. Used for XS1601 labor share.]</t>
         </is>
@@ -1588,7 +1673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1748,6 +1833,18 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>validator_class</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>tautological</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/XS1602.xlsx
+++ b/extenbooks/XS1602.xlsx
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Main finding of Karabacak &amp; Tonak (2022): NSW was NEGATIVE for all 40 years (1980-2019). Mean NSW/GDP = -0.0113 (-1.13% of GDP). Paper reports -0.011 (rounded). ST2 series XS1602 achieves mean = -0.0098 after [internal-decision-record] fix (TurkStat labor share replaces SBB proxy). The remaining gap of ~0.0015 is attributable to: (a) the 2007-2019 period having NaN values in XS1602 (reducing the denominator of the mean), (b) TurkStat Table 20.37 economy-wide ls vs. the paper's productive-sector ls, and (c) benefit/tax level data not yet fully disaggregated from Turkish ministry sources. The direction, sign, and order of magnitude match the paper.</t>
+          <t>Main finding of Karabacak &amp; Tonak (2022): NSW was NEGATIVE for all 40 years (1980-2019). Mean NSW/GDP = -0.0113 (-1.13% of GDP). Paper reports -0.011 (rounded). predecessor-build series XS1602 achieves mean = -0.0098 after [internal-decision-record] fix (TurkStat labor share replaces SBB proxy). The remaining gap of ~0.0015 is attributable to: (a) the 2007-2019 period having NaN values in XS1602 (reducing the denominator of the mean), (b) TurkStat Table 20.37 economy-wide ls vs. the paper's productive-sector ls, and (c) benefit/tax level data not yet fully disaggregated from Turkish ministry sources. The direction, sign, and order of magnitude match the paper.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NSW was negative for ALL 40 years (1980-2019) — 100% of observations. No year had a positive NSW. This is the central empirical claim of KT (2022): the Turkish 'pseudo-welfare state' extracts more from workers than it returns. ST2 XS1602 must reproduce this universal-negative property. Any year with a computed positive value should be flagged as a data error, not accepted as consistent with the source.</t>
+          <t>NSW was negative for ALL 40 years (1980-2019) — 100% of observations. No year had a positive NSW. This is the central empirical claim of KT (2022): the Turkish 'pseudo-welfare state' extracts more from workers than it returns. predecessor-build XS1602 must reproduce this universal-negative property. Any year with a computed positive value should be flagged as a data error, not accepted as consistent with the source.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Validation benchmark: KT (2022) Abstract and Section 5.1 report mean NSW/GDP = -0.0113 (stated as '-1.13% of GDP'). The paper rounds to '-1.1%' in the Abstract. ST2 achieves -0.0098 after [internal-decision-record] fix. The 0.0015 residual gap is acceptable given: (a) TurkStat total-compensation ls vs. paper's productive-sector ls, (b) 2007-2019 NaN years affecting the mean, (c) benefit/tax source data provenance differences. The sign (negative) and universal negativity (100% of years) are the primary validation criteria. V-layer acceptance range: [-0.008, -0.015].</t>
+          <t>Validation benchmark: KT (2022) Abstract and Section 5.1 report mean NSW/GDP = -0.0113 (stated as '-1.13% of GDP'). The paper rounds to '-1.1%' in the Abstract. predecessor-build achieves -0.0098 after [internal-decision-record] fix. The 0.0015 residual gap is acceptable given: (a) TurkStat total-compensation ls vs. paper's productive-sector ls, (b) 2007-2019 NaN years affecting the mean, (c) benefit/tax source data provenance differences. The sign (negative) and universal negativity (100% of years) are the primary validation criteria. V-layer acceptance range: [-0.008, -0.015].</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1590,7 +1590,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mean residual: ST2 achieves -0.0098 vs. paper's -0.011. Gap of 0.0015 is within acceptable range given ls methodology differences (total compensation / GDP vs. productive-sector wages / NDP).</t>
+          <t>Mean residual: predecessor-build achieves -0.0098 vs. paper's -0.011. Gap of 0.0015 is within acceptable range given ls methodology differences (total compensation / GDP vs. productive-sector wages / NDP).</t>
         </is>
       </c>
     </row>
